--- a/bakup/customers.xlsx
+++ b/bakup/customers.xlsx
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2575000</v>
+        <v>2833000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/06/02 - 19:41</t>
+          <t>1405/07/17 - 17:48</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5639000</v>
+        <v>7216000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/06/02 - 19:41</t>
+          <t>1405/07/19 - 18:09</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3677000</v>
+        <v>2730000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/06/05 - 15:34</t>
+          <t>1405/07/21 - 16:43</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>518000</v>
+        <v>-9000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/06/02 - 19:42</t>
+          <t>1405/07/17 - 17:44</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>220000</v>
+        <v>150000</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1405/06/05 - 15:35</t>
+          <t>1405/06/22 - 09:58</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3610000</v>
+        <v>3965000</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1405/06/05 - 15:38</t>
+          <t>1405/07/10 - 19:20</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>866500</v>
+        <v>2363500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/06/01 - 16:49</t>
+          <t>1405/07/21 - 16:45</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2924600</v>
+        <v>3282600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/06/05 - 15:37</t>
+          <t>1405/07/03 - 15:20</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1500000</v>
+        <v>2115000</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1405/06/04 - 18:38</t>
+          <t>1405/07/21 - 16:45</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -730,11 +730,11 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4891000</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1405/05/31 - 16:57</t>
+          <t>1405/07/17 - 15:46</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>425000</v>
+        <v>600000</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1405/06/02 - 11:28</t>
+          <t>1405/07/19 - 16:22</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -767,11 +767,27 @@
       </c>
     </row>
     <row r="16" ht="27.75" customHeight="1">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="A16" s="3" t="n">
+        <v>3011</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>علی رحمتی</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1887000</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>1405/07/19 - 19:05</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ali.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
       <c r="A17" s="3" t="n"/>
